--- a/Sample_run/1/student/KienTTHE186727/TC2/GradeDetail.xlsx
+++ b/Sample_run/1/student/KienTTHE186727/TC2/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>38098</x:v>
+        <x:v>36288</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1097,7 +1097,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>38098</x:v>
+        <x:v>36288</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>38098</x:v>
+        <x:v>36288</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1206,7 +1206,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35914</x:v>
+        <x:v>42870</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1265,7 +1265,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35914</x:v>
+        <x:v>42870</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>54</x:v>
@@ -1318,7 +1318,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>35914</x:v>
+        <x:v>42870</x:v>
       </x:c>
       <x:c r="Q7" s="0">
         <x:v>4000</x:v>
@@ -1374,7 +1374,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>38098</x:v>
+        <x:v>36288</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1433,7 +1433,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>38098</x:v>
+        <x:v>36288</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>54</x:v>
